--- a/dance_registration_forms/022_dance_class_enrollment_form--dance_registration_forms.xlsx
+++ b/dance_registration_forms/022_dance_class_enrollment_form--dance_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'credit_card',_'value':_'credit-card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Credit Card', 'value': 'credit-card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'debit_card',_'value':_'debit-card'}</t>
+          <t>debit_card</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Debit Card', 'value': 'debit-card'}</t>
+          <t>Debit Card</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bank_transfer',_'value':_'bank-transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bank Transfer', 'value': 'bank-transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cash',_'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cash', 'value': 'cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'paid',_'value':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Paid', 'value': 'paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unpaid',_'value':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unpaid', 'value': 'unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'partially_paid',_'value':_'partially-paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Partially Paid', 'value': 'partially-paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning', 'value': 'morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon', 'value': 'afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening', 'value': 'evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Confirmed', 'value': 'confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_confirmed',_'value':_'not-confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Confirmed', 'value': 'not-confirmed'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'confirmed',_'value':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Confirmed', 'value': 'confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_confirmed',_'value':_'not-confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Confirmed', 'value': 'not-confirmed'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
